--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486512_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486512_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8213</v>
+        <v>0.9639</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4152</v>
+        <v>0.5269</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4061</v>
+        <v>0.4369</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8448</v>
@@ -610,13 +610,13 @@
         <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1164</v>
+        <v>0.0261</v>
       </c>
       <c r="T2" t="n">
-        <v>0.012</v>
+        <v>0.1238</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1636</v>
+        <v>0.7719</v>
       </c>
       <c r="E3" t="n">
-        <v>1.313</v>
+        <v>1.7673</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1495</v>
+        <v>-0.9954</v>
       </c>
       <c r="G3" t="n">
         <v>-2.6448</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.1673</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3509</v>
+        <v>0.1034</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4248</v>
+        <v>-0.2707</v>
       </c>
       <c r="V3" t="n">
         <v>1.1915</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>M. NUGU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6419</v>
+        <v>0.1748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6727</v>
+        <v>1.9289</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3146</v>
+        <v>-1.7542</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.5002</v>
+        <v>0.4821</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.4116</v>
+        <v>0.9674</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.0886</v>
+        <v>-0.4853</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.7055</v>
+        <v>3.7278</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2497</v>
+        <v>2.1963</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4558</v>
+        <v>1.5316</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.7948</v>
+        <v>-3.2458</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1619</v>
+        <v>-1.2289</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.6328</v>
+        <v>-2.0169</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4801</v>
+        <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5761</v>
+        <v>-0.0898</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2508</v>
+        <v>0.3761</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3253</v>
+        <v>-0.466</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0647</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3899</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7454</v>
+        <v>-1.1372</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8426</v>
+        <v>1.2658</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5879</v>
+        <v>-2.403</v>
       </c>
       <c r="G5" t="n">
         <v>-1.6527</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0221</v>
+        <v>-0.414</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6802</v>
+        <v>0.1034</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7023</v>
+        <v>-0.5173</v>
       </c>
       <c r="V5" t="n">
         <v>1.582</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NUGU</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9257</v>
+        <v>-1.3731</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6743</v>
+        <v>-0.8353</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4821</v>
+        <v>-1.8737</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9674</v>
+        <v>-0.9398</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4853</v>
+        <v>-0.9339</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7278</v>
+        <v>-0.6903</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1963</v>
+        <v>-0.6903</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5316</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2458</v>
+        <v>-1.1834</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2289</v>
+        <v>-0.2495</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0169</v>
+        <v>-0.9339</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1903</v>
+        <v>-0.1944</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8784</v>
+        <v>-0.1875</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3118</v>
+        <v>-0.0069</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1775</v>
+        <v>-1.4907</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1405</v>
+        <v>-1.8054</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.318</v>
+        <v>0.3147</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7775</v>
+        <v>-1.3276</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5694</v>
+        <v>-0.663</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.208</v>
+        <v>-0.6646</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8617</v>
+        <v>-0.7107</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6721</v>
+        <v>0.1674</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1896</v>
+        <v>-0.8781</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9158</v>
+        <v>-0.6169</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8974</v>
+        <v>-0.8304</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0184</v>
+        <v>0.2136</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9475</v>
+        <v>-0.1631</v>
       </c>
       <c r="T7" t="n">
-        <v>2.0898</v>
+        <v>-0.0072</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1423</v>
+        <v>-0.1559</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6343</v>
+        <v>-1.4908</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1273</v>
+        <v>0.5164</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.507</v>
+        <v>-2.0072</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8737</v>
+        <v>-3.0824</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9398</v>
+        <v>-2.1198</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9339</v>
+        <v>-0.9626</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6903</v>
+        <v>-0.8176</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6903</v>
+        <v>-1.1069</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.2893</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1834</v>
+        <v>-2.2648</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2495</v>
+        <v>-1.0129</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9339</v>
+        <v>-1.2519</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>2.6101</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4556</v>
+        <v>0.1821</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4795</v>
+        <v>-0.0336</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0239</v>
+        <v>0.2157</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>-0.113</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>2.4552</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.5682</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7952</v>
+        <v>-1.6032</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1407</v>
+        <v>-0.1962</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3456</v>
+        <v>-1.407</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3276</v>
+        <v>-5.5002</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.663</v>
+        <v>-2.4116</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6646</v>
+        <v>-3.0886</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7107</v>
+        <v>-1.7055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1674</v>
+        <v>-1.2497</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8781</v>
+        <v>-0.4558</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6169</v>
+        <v>-3.7948</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8304</v>
+        <v>-1.1619</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2136</v>
+        <v>-2.6328</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>3.4801</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4676</v>
+        <v>1.6148</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>1.382</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1251</v>
+        <v>0.2328</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.0647</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.3899</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2358</v>
+        <v>-1.9237</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7773</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4586</v>
+        <v>-1.1954</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4642</v>
+        <v>-2.862</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4562</v>
+        <v>-1.3503</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.008</v>
+        <v>-1.5117</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1677</v>
+        <v>-0.0481</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0912</v>
+        <v>-0.8514</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0765</v>
+        <v>0.8032</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.632</v>
+        <v>-2.8138</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5475</v>
+        <v>-0.4989</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-2.3149</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1164</v>
+        <v>0.0682</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2055</v>
+        <v>0.4074</v>
       </c>
       <c r="U10" t="n">
-        <v>0.089</v>
+        <v>-0.3392</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7427</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2482</v>
+        <v>-2.068</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1794</v>
+        <v>-0.6403</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0688</v>
+        <v>-1.4277</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0824</v>
+        <v>-0.4642</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1198</v>
+        <v>-0.4562</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9626</v>
+        <v>-0.008</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8176</v>
+        <v>0.1677</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1069</v>
+        <v>0.0912</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2893</v>
+        <v>0.0765</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2648</v>
+        <v>-0.632</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0129</v>
+        <v>-0.5475</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2519</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6101</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5754</v>
+        <v>0.0514</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7294</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1541</v>
+        <v>0.1199</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.113</v>
+        <v>-2.7427</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4552</v>
+        <v>-0.7395</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5682</v>
+        <v>-2.0032</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6186</v>
+        <v>-2.6419</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2691</v>
+        <v>-1.2006</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3495</v>
+        <v>-1.4413</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.862</v>
+        <v>-2.7775</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3503</v>
+        <v>-1.5694</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5117</v>
+        <v>-1.208</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0481</v>
+        <v>-0.8617</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8514</v>
+        <v>-0.6721</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8032</v>
+        <v>-0.1896</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8138</v>
+        <v>-1.9158</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4989</v>
+        <v>-0.8974</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.3149</v>
+        <v>-1.0184</v>
       </c>
       <c r="P12" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6267</v>
+        <v>0.4831</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1334</v>
+        <v>0.7487</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4933</v>
+        <v>-0.2656</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3528</v>
+        <v>-4.86</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1063</v>
+        <v>-1.4286</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2465</v>
+        <v>-3.4314</v>
       </c>
       <c r="G13" t="n">
         <v>-7.0556</v>
@@ -1468,13 +1468,13 @@
         <v>3.0451</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0993</v>
+        <v>0.3936</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3268</v>
+        <v>0.3509</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2276</v>
+        <v>0.0427</v>
       </c>
       <c r="V13" t="n">
         <v>-1.243</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.3905</v>
+        <v>-16.678</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.541799999999999</v>
+        <v>-0.8293999999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.8487</v>
+        <v>-15.8488</v>
       </c>
       <c r="G14" t="n">
         <v>-29.6034</v>
@@ -1522,7 +1522,7 @@
         <v>-2.963200000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8039999999999999</v>
+        <v>-0.8040000000000006</v>
       </c>
       <c r="L14" t="n">
         <v>-2.1593</v>
@@ -1546,22 +1546,22 @@
         <v>21.7506</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07809999999999989</v>
+        <v>1.7907</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5864</v>
+        <v>3.2989</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5082</v>
+        <v>-1.5081</v>
       </c>
       <c r="V14" t="n">
-        <v>2.434499999999999</v>
+        <v>2.434500000000001</v>
       </c>
       <c r="W14" t="n">
         <v>11.8855</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.451000000000001</v>
+        <v>-9.450999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.2742</v>
+        <v>10.9884</v>
       </c>
       <c r="E15" t="n">
-        <v>9.622999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6512</v>
+        <v>0.9184</v>
       </c>
       <c r="G15" t="n">
         <v>11.2542</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5397</v>
+        <v>0.1745</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.262</v>
+        <v>0.1851</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2777</v>
+        <v>-0.0105</v>
       </c>
       <c r="V15" t="n">
         <v>0.6472</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6456</v>
+        <v>5.7624</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1511</v>
+        <v>2.8159</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4944</v>
+        <v>2.9466</v>
       </c>
       <c r="G16" t="n">
         <v>3.5086</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0583</v>
+        <v>0.0586</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5516</v>
+        <v>0.2163</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6099</v>
+        <v>-0.1577</v>
       </c>
       <c r="V16" t="n">
         <v>1.3252</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4958</v>
+        <v>4.5902</v>
       </c>
       <c r="E17" t="n">
-        <v>5.3468</v>
+        <v>4.5645</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1489</v>
+        <v>0.0257</v>
       </c>
       <c r="G17" t="n">
         <v>3.1195</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5088</v>
+        <v>0.6032</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2966</v>
+        <v>0.5143</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2122</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>2.8249</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1923</v>
+        <v>4.5597</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7033</v>
+        <v>0.9268</v>
       </c>
       <c r="F18" t="n">
-        <v>3.489</v>
+        <v>3.6329</v>
       </c>
       <c r="G18" t="n">
         <v>3.3722</v>
@@ -1858,13 +1858,13 @@
         <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2674</v>
+        <v>0.1</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3305</v>
+        <v>-0.1069</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0631</v>
+        <v>0.207</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4677</v>
+        <v>2.9559</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.395</v>
+        <v>3.2025</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8626</v>
+        <v>-0.2466</v>
       </c>
       <c r="G19" t="n">
-        <v>5.2763</v>
+        <v>2.5591</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8618</v>
+        <v>1.1678</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4144</v>
+        <v>1.3913</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0149</v>
+        <v>3.2358</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1352</v>
+        <v>1.5512</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8797</v>
+        <v>1.6846</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2614</v>
+        <v>-0.6767</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7267</v>
+        <v>-0.3834</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5347</v>
+        <v>-0.2933</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2383</v>
+        <v>0.2923</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3425</v>
+        <v>-0.0757</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1042</v>
+        <v>0.368</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0477</v>
+        <v>-0.113</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
         <v>-1.243</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3792</v>
+        <v>2.8967</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8672</v>
+        <v>-0.1714</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4881</v>
+        <v>3.0682</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5591</v>
+        <v>5.2763</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1678</v>
+        <v>2.8618</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3913</v>
+        <v>2.4144</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2358</v>
+        <v>3.0149</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5512</v>
+        <v>2.1352</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6846</v>
+        <v>0.8797</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6767</v>
+        <v>2.2614</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3834</v>
+        <v>0.7267</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2933</v>
+        <v>1.5347</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2844</v>
+        <v>0.1908</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.411</v>
+        <v>-0.119</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1265</v>
+        <v>0.3097</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.113</v>
+        <v>-1.0477</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
         <v>-1.243</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5661</v>
+        <v>1.4313</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1014</v>
+        <v>1.2132</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4647</v>
+        <v>0.2181</v>
       </c>
       <c r="G21" t="n">
         <v>1.2086</v>
@@ -2092,13 +2092,13 @@
         <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2105</v>
+        <v>0.0757</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.416</v>
+        <v>0.1694</v>
       </c>
       <c r="V21" t="n">
         <v>1.017</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>C. BARTON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9933</v>
+        <v>-0.6319</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6089</v>
+        <v>0.6763</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6023</v>
+        <v>-1.3083</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8562</v>
+        <v>2.068</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1527</v>
+        <v>0.9245</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0089</v>
+        <v>1.1435</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5424</v>
+        <v>1.5103</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6538</v>
+        <v>0.4959</v>
       </c>
       <c r="L22" t="n">
-        <v>3.1962</v>
+        <v>1.0144</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6863</v>
+        <v>0.5577</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4989</v>
+        <v>0.4286</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1873</v>
+        <v>0.1291</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.519</v>
+        <v>0.125</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.411</v>
+        <v>0.2536</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.108</v>
+        <v>-0.1286</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.678</v>
+        <v>-2.8249</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.243</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. BARTON</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2023</v>
+        <v>-0.8508</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2293</v>
+        <v>1.7207</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4316</v>
+        <v>-2.5714</v>
       </c>
       <c r="G23" t="n">
-        <v>2.068</v>
+        <v>0.8562</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9245</v>
+        <v>-1.1527</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1435</v>
+        <v>2.0089</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5103</v>
+        <v>2.5424</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4959</v>
+        <v>-0.6538</v>
       </c>
       <c r="L23" t="n">
-        <v>1.0144</v>
+        <v>3.1962</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5577</v>
+        <v>-1.6863</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4286</v>
+        <v>-0.4989</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1291</v>
+        <v>-1.1873</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4454</v>
+        <v>-0.3764</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1935</v>
+        <v>-0.2992</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2519</v>
+        <v>-0.0772</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.8249</v>
+        <v>-0.678</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.8249</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8434</v>
+        <v>-2.2287</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.019</v>
+        <v>-1.466</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8243</v>
+        <v>-0.7627</v>
       </c>
       <c r="G24" t="n">
         <v>-0.275</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6492</v>
+        <v>0.2638</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7571</v>
+        <v>0.31</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3788</v>
+        <v>-4.1989</v>
       </c>
       <c r="E25" t="n">
         <v>-3.7674</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.4316</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8326</v>
@@ -2404,13 +2404,13 @@
         <v>1.305</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0035</v>
+        <v>0.1763</v>
       </c>
       <c r="T25" t="n">
         <v>0.4266</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4301</v>
+        <v>-0.2503</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4552</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.2126</v>
+        <v>-5.3937</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.601</v>
+        <v>-3.9363</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6116</v>
+        <v>-1.4574</v>
       </c>
       <c r="G26" t="n">
         <v>-2.5117</v>
@@ -2482,13 +2482,13 @@
         <v>0.87</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0907</v>
+        <v>-0.2719</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6321</v>
+        <v>0.2968</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7228</v>
+        <v>-0.5687</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>18.3905</v>
+        <v>19.8806</v>
       </c>
       <c r="E27" t="n">
-        <v>15.8486</v>
+        <v>15.8488</v>
       </c>
       <c r="F27" t="n">
-        <v>2.541500000000001</v>
+        <v>4.0319</v>
       </c>
       <c r="G27" t="n">
         <v>29.6034</v>
@@ -2545,7 +2545,7 @@
         <v>2.9631</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8038</v>
+        <v>0.8038000000000002</v>
       </c>
       <c r="O27" t="n">
         <v>2.1592</v>
@@ -2560,19 +2560,19 @@
         <v>13.0502</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0782000000000001</v>
+        <v>1.4119</v>
       </c>
       <c r="T27" t="n">
-        <v>1.508</v>
+        <v>1.5082</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.5863</v>
+        <v>-0.09630000000000022</v>
       </c>
       <c r="V27" t="n">
         <v>-2.4345</v>
       </c>
       <c r="W27" t="n">
-        <v>9.450900000000001</v>
+        <v>9.450899999999999</v>
       </c>
       <c r="X27" t="n">
         <v>-11.8855</v>
